--- a/input/stock.xlsx
+++ b/input/stock.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dratw\Documents\codes\priceChecker\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D327E6-8D4D-41AF-B8C0-DB5B328DCBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94DAB54-0A04-49C2-BB45-D5A7267F44D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hold" sheetId="23" r:id="rId1"/>
-    <sheet name="expected" sheetId="24" r:id="rId2"/>
+    <sheet name="expected1" sheetId="24" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="38">
   <si>
     <t>size</t>
   </si>
@@ -46,22 +46,106 @@
     <t>FZ5896</t>
   </si>
   <si>
-    <t>1135092-DRI</t>
-  </si>
-  <si>
     <t>554724-174</t>
   </si>
   <si>
     <t>BB550PB1</t>
   </si>
   <si>
-    <t>DZ4706-200</t>
-  </si>
-  <si>
     <t>10W</t>
   </si>
   <si>
-    <t>price</t>
+    <t>price_net</t>
+  </si>
+  <si>
+    <t>BD7633</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>FZ5904</t>
+  </si>
+  <si>
+    <t>DC0774-141</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>DZ5485-303</t>
+  </si>
+  <si>
+    <t>CT8012-116</t>
+  </si>
+  <si>
+    <t>DD1399-105</t>
+  </si>
+  <si>
+    <t>DD1503-200</t>
+  </si>
+  <si>
+    <t>10.5W</t>
+  </si>
+  <si>
+    <t>DV4024-002</t>
+  </si>
+  <si>
+    <t>6.5W</t>
+  </si>
+  <si>
+    <t>9.5W</t>
+  </si>
+  <si>
+    <t>DD1391-103</t>
+  </si>
+  <si>
+    <t>DQ7576-001</t>
+  </si>
+  <si>
+    <t>9W</t>
+  </si>
+  <si>
+    <t>11W</t>
+  </si>
+  <si>
+    <t>12W</t>
+  </si>
+  <si>
+    <t>DD1873-102</t>
+  </si>
+  <si>
+    <t>6W</t>
+  </si>
+  <si>
+    <t>7.5W</t>
+  </si>
+  <si>
+    <t>8W</t>
+  </si>
+  <si>
+    <t>8.5W</t>
+  </si>
+  <si>
+    <t>DN1431-102</t>
+  </si>
+  <si>
+    <t>CW1590-100</t>
+  </si>
+  <si>
+    <t>DD1503-101</t>
+  </si>
+  <si>
+    <t>DO9457-100</t>
+  </si>
+  <si>
+    <t>DD1503-109</t>
+  </si>
+  <si>
+    <t>DD1391-402</t>
+  </si>
+  <si>
+    <t>6Y</t>
   </si>
 </sst>
 </file>
@@ -401,12 +485,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C3ED77E-355F-451A-8EC6-B2847837F9C7}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -418,40 +502,1635 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>773</v>
+        <v>323.89999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>299</v>
+        <v>323.89999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>323.89999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>323.89999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>323.89999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>323.89999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C13">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17">
         <v>8</v>
       </c>
-      <c r="C4">
-        <v>549</v>
+      <c r="C17">
+        <v>473.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>473.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>473.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>473.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>903.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <v>493.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24">
+        <v>493.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>493.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>493.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>493.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34">
+        <v>6</v>
+      </c>
+      <c r="C34">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>26</v>
+      </c>
+      <c r="B66" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B67" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>26</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>26</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>26</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2</v>
+      </c>
+      <c r="C70">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>26</v>
+      </c>
+      <c r="B71" t="s">
+        <v>28</v>
+      </c>
+      <c r="C71">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>26</v>
+      </c>
+      <c r="B72" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>26</v>
+      </c>
+      <c r="B73" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>26</v>
+      </c>
+      <c r="B75" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>26</v>
+      </c>
+      <c r="B76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>26</v>
+      </c>
+      <c r="B77" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>26</v>
+      </c>
+      <c r="B78" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>26</v>
+      </c>
+      <c r="B79" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>26</v>
+      </c>
+      <c r="B80" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>26</v>
+      </c>
+      <c r="B81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>26</v>
+      </c>
+      <c r="B82" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>26</v>
+      </c>
+      <c r="B83" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>26</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>26</v>
+      </c>
+      <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>26</v>
+      </c>
+      <c r="B86" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>26</v>
+      </c>
+      <c r="B87" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>26</v>
+      </c>
+      <c r="B88" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>26</v>
+      </c>
+      <c r="B89" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>26</v>
+      </c>
+      <c r="B90" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>26</v>
+      </c>
+      <c r="B91" t="s">
+        <v>28</v>
+      </c>
+      <c r="C91">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>26</v>
+      </c>
+      <c r="B92" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>26</v>
+      </c>
+      <c r="B93" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>26</v>
+      </c>
+      <c r="B94" t="s">
+        <v>28</v>
+      </c>
+      <c r="C94">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>26</v>
+      </c>
+      <c r="B95" t="s">
+        <v>28</v>
+      </c>
+      <c r="C95">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>26</v>
+      </c>
+      <c r="B96" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>26</v>
+      </c>
+      <c r="B97" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>26</v>
+      </c>
+      <c r="B98" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>26</v>
+      </c>
+      <c r="B99" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>26</v>
+      </c>
+      <c r="B100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>26</v>
+      </c>
+      <c r="B101" t="s">
+        <v>30</v>
+      </c>
+      <c r="C101">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>26</v>
+      </c>
+      <c r="B102" t="s">
+        <v>30</v>
+      </c>
+      <c r="C102">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>26</v>
+      </c>
+      <c r="B103" t="s">
+        <v>30</v>
+      </c>
+      <c r="C103">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>26</v>
+      </c>
+      <c r="B104" t="s">
+        <v>30</v>
+      </c>
+      <c r="C104">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>26</v>
+      </c>
+      <c r="B105" t="s">
+        <v>30</v>
+      </c>
+      <c r="C105">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>26</v>
+      </c>
+      <c r="B106" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>26</v>
+      </c>
+      <c r="B107" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>26</v>
+      </c>
+      <c r="B108" t="s">
+        <v>30</v>
+      </c>
+      <c r="C108">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>26</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>31</v>
+      </c>
+      <c r="B110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>31</v>
+      </c>
+      <c r="B111" t="s">
+        <v>19</v>
+      </c>
+      <c r="C111">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>31</v>
+      </c>
+      <c r="B112" t="s">
+        <v>19</v>
+      </c>
+      <c r="C112">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>31</v>
+      </c>
+      <c r="B113" t="s">
+        <v>19</v>
+      </c>
+      <c r="C113">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>31</v>
+      </c>
+      <c r="B114" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>31</v>
+      </c>
+      <c r="B115" t="s">
+        <v>28</v>
+      </c>
+      <c r="C115">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>31</v>
+      </c>
+      <c r="B116" t="s">
+        <v>30</v>
+      </c>
+      <c r="C116">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>31</v>
+      </c>
+      <c r="B117" t="s">
+        <v>23</v>
+      </c>
+      <c r="C117">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>32</v>
+      </c>
+      <c r="B118" t="s">
+        <v>37</v>
+      </c>
+      <c r="C118">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" t="s">
+        <v>29</v>
+      </c>
+      <c r="C119">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>33</v>
+      </c>
+      <c r="B120" t="s">
+        <v>29</v>
+      </c>
+      <c r="C120">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>34</v>
+      </c>
+      <c r="B121" t="s">
+        <v>28</v>
+      </c>
+      <c r="C121">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>34</v>
+      </c>
+      <c r="B122" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>34</v>
+      </c>
+      <c r="B123" t="s">
+        <v>30</v>
+      </c>
+      <c r="C123">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>34</v>
+      </c>
+      <c r="B124" t="s">
+        <v>23</v>
+      </c>
+      <c r="C124">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>34</v>
+      </c>
+      <c r="B125" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>35</v>
+      </c>
+      <c r="B126" t="s">
+        <v>19</v>
+      </c>
+      <c r="C126">
+        <v>378.99</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>35</v>
+      </c>
+      <c r="B127" t="s">
+        <v>19</v>
+      </c>
+      <c r="C127">
+        <v>378.99</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>35</v>
+      </c>
+      <c r="B128" t="s">
+        <v>19</v>
+      </c>
+      <c r="C128">
+        <v>378.99</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>35</v>
+      </c>
+      <c r="B129" t="s">
+        <v>19</v>
+      </c>
+      <c r="C129">
+        <v>378.99</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>35</v>
+      </c>
+      <c r="B130" t="s">
+        <v>19</v>
+      </c>
+      <c r="C130">
+        <v>378.99</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>35</v>
+      </c>
+      <c r="B131" t="s">
+        <v>19</v>
+      </c>
+      <c r="C131">
+        <v>378.99</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>35</v>
+      </c>
+      <c r="B132" t="s">
+        <v>19</v>
+      </c>
+      <c r="C132">
+        <v>378.99</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>35</v>
+      </c>
+      <c r="B133" t="s">
+        <v>19</v>
+      </c>
+      <c r="C133">
+        <v>378.99</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>35</v>
+      </c>
+      <c r="B134" t="s">
+        <v>28</v>
+      </c>
+      <c r="C134">
+        <v>378.99</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>36</v>
+      </c>
+      <c r="B135" t="s">
+        <v>12</v>
+      </c>
+      <c r="C135">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>36</v>
+      </c>
+      <c r="B136" t="s">
+        <v>12</v>
+      </c>
+      <c r="C136">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>36</v>
+      </c>
+      <c r="B137" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>36</v>
+      </c>
+      <c r="B138" t="s">
+        <v>12</v>
+      </c>
+      <c r="C138">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>36</v>
+      </c>
+      <c r="B139" t="s">
+        <v>12</v>
+      </c>
+      <c r="C139">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>36</v>
+      </c>
+      <c r="B140" t="s">
+        <v>12</v>
+      </c>
+      <c r="C140">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>36</v>
+      </c>
+      <c r="B141" t="s">
+        <v>12</v>
+      </c>
+      <c r="C141">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>36</v>
+      </c>
+      <c r="B142" t="s">
+        <v>12</v>
+      </c>
+      <c r="C142">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>36</v>
+      </c>
+      <c r="B143" t="s">
+        <v>12</v>
+      </c>
+      <c r="C143">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>36</v>
+      </c>
+      <c r="B144" t="s">
+        <v>12</v>
+      </c>
+      <c r="C144">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>36</v>
+      </c>
+      <c r="B145" t="s">
+        <v>12</v>
+      </c>
+      <c r="C145">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>36</v>
+      </c>
+      <c r="B146">
+        <v>8</v>
+      </c>
+      <c r="C146">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>36</v>
+      </c>
+      <c r="B147">
+        <v>14</v>
+      </c>
+      <c r="C147">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148">
+        <v>7</v>
+      </c>
+      <c r="C148">
+        <v>447.14634146341467</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>5</v>
+      </c>
+      <c r="B149">
+        <v>7</v>
+      </c>
+      <c r="C149">
+        <v>447.14634146341467</v>
       </c>
     </row>
   </sheetData>
@@ -462,37 +2141,145 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E5512D-63D6-4854-A13F-1543E21BBB98}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>503.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>283.98373983739839</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>283.98373983739839</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>283.98373983739839</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>283.98373983739839</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>283.98373983739839</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>283.98373983739839</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>283.98373983739839</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>283.98373983739839</v>
       </c>
     </row>
   </sheetData>
